--- a/data/trans_orig/IP05A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A01-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>44904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61583</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50705</t>
+          <t>50024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68051</t>
+          <t>68495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100519</t>
+          <t>101113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125763</t>
+          <t>124041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>47389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38443</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55805</t>
+          <t>55719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73553</t>
+          <t>74706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96176</t>
+          <t>97975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119186</t>
+          <t>119478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144800</t>
+          <t>145948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113463</t>
+          <t>113077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138183</t>
+          <t>138749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240211</t>
+          <t>241301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275975</t>
+          <t>277064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>80527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>106160</t>
+          <t>105991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>118830</t>
+          <t>118410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>181816</t>
+          <t>182403</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>217414</t>
+          <t>218293</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37276</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>58452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73206</t>
+          <t>72714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65871</t>
+          <t>65139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85708</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126220</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152354</t>
+          <t>150760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42558</t>
+          <t>43411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>59523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89788</t>
+          <t>90580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115699</t>
+          <t>116131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83857</t>
+          <t>83008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105434</t>
+          <t>105184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93344</t>
+          <t>91715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115688</t>
+          <t>115966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182286</t>
+          <t>181380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213991</t>
+          <t>214636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87217</t>
+          <t>87336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67439</t>
+          <t>67876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90701</t>
+          <t>91496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141908</t>
+          <t>140978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172872</t>
+          <t>172040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30100</t>
+          <t>30720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>54924</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323385</t>
+          <t>323949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365850</t>
+          <t>366486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342348</t>
+          <t>342035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>384980</t>
+          <t>384899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>676747</t>
+          <t>679411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>738378</t>
+          <t>740120</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240528</t>
+          <t>240003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>279749</t>
+          <t>280691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>263387</t>
+          <t>263559</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>306490</t>
+          <t>305865</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>515998</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>573587</t>
+          <t>572135</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>62918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89801</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86700</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>132373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167863</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90831</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108935</t>
+          <t>109205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101050</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118551</t>
+          <t>118747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198286</t>
+          <t>198175</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223311</t>
+          <t>222858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>27123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>43560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>55004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77713</t>
+          <t>77543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23562</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162203</t>
+          <t>161743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183218</t>
+          <t>183831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169943</t>
+          <t>169719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194531</t>
+          <t>195388</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339805</t>
+          <t>338221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373723</t>
+          <t>373009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59826</t>
+          <t>60233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82969</t>
+          <t>83248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102317</t>
+          <t>103285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134831</t>
+          <t>135684</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96968</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117600</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100149</t>
+          <t>99371</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118997</t>
+          <t>118212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>203420</t>
+          <t>201929</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>229853</t>
+          <t>228118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28378</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46608</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29424</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46792</t>
+          <t>47883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88681</t>
+          <t>87560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98529</t>
+          <t>100166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119856</t>
+          <t>121290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119008</t>
+          <t>118318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138440</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223554</t>
+          <t>223073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252758</t>
+          <t>252926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57791</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49776</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75031</t>
+          <t>74789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101923</t>
+          <t>101845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>16749</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>469831</t>
+          <t>469710</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>510101</t>
+          <t>510833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>510562</t>
+          <t>511230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>551618</t>
+          <t>551502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>992589</t>
+          <t>987403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1051560</t>
+          <t>1050925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>150928</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>188563</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>159966</t>
+          <t>160620</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>199485</t>
+          <t>199076</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>322517</t>
+          <t>323916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>374905</t>
+          <t>378261</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>54484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77907</t>
+          <t>76671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>108353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87111</t>
+          <t>87493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103543</t>
+          <t>103880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87041</t>
+          <t>88105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102418</t>
+          <t>103353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180642</t>
+          <t>179415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202767</t>
+          <t>202151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>34334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59390</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142459</t>
+          <t>144225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162747</t>
+          <t>164573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>180985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201962</t>
+          <t>203218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330086</t>
+          <t>329573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>361022</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41892</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>62737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87782</t>
+          <t>87793</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>115460</t>
+          <t>116104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>30535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135790</t>
+          <t>137896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155460</t>
+          <t>155398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130274</t>
+          <t>131453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150690</t>
+          <t>150412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>274131</t>
+          <t>274108</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>301724</t>
+          <t>300819</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>25434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>41641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>26473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81326</t>
+          <t>81100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>29149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>109657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129947</t>
+          <t>129538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101300</t>
+          <t>101078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122704</t>
+          <t>122767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216472</t>
+          <t>217701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247075</t>
+          <t>247066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41126</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>62585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78472</t>
+          <t>78205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105243</t>
+          <t>106023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>498193</t>
+          <t>497520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>535248</t>
+          <t>534620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>520398</t>
+          <t>520794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561319</t>
+          <t>561133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1027975</t>
+          <t>1031424</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1087717</t>
+          <t>1086688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131182</t>
+          <t>131657</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167669</t>
+          <t>166608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142154</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>180062</t>
+          <t>179578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>285007</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>335323</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49561</t>
+          <t>48538</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95610</t>
+          <t>95949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52969</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42237</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>52778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90496</t>
+          <t>90682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118038</t>
+          <t>118979</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134321</t>
+          <t>134836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133607</t>
+          <t>133165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150997</t>
+          <t>151304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258718</t>
+          <t>257684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281966</t>
+          <t>282236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25512</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>35682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58121</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125195</t>
+          <t>126589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144615</t>
+          <t>145613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>153854</t>
+          <t>154518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179027</t>
+          <t>179115</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286353</t>
+          <t>289229</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>318266</t>
+          <t>318894</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40963</t>
+          <t>40173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24067</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>46539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81701</t>
+          <t>79466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>16870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26724</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135888</t>
+          <t>139482</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>224000</t>
+          <t>222785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238159</t>
+          <t>238693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>265907</t>
+          <t>265634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381892</t>
+          <t>372183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480963</t>
+          <t>479977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132679</t>
+          <t>130874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>48461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74037</t>
+          <t>74802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177379</t>
+          <t>185579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>26233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>443413</t>
+          <t>443232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>539362</t>
+          <t>540857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>591604</t>
+          <t>588423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>632453</t>
+          <t>633833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1051606</t>
+          <t>1048628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1159720</t>
+          <t>1160105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>95807</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196632</t>
+          <t>199282</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>88434</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125982</t>
+          <t>128318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>197853</t>
+          <t>197631</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>310250</t>
+          <t>311434</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
